--- a/event_planner_forms/018_laser_tag_online_booking_form--event_planner_forms.xlsx
+++ b/event_planner_forms/018_laser_tag_online_booking_form--event_planner_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,64 +510,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>event_planner_form</t>
+          <t>event_form_title</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Event Planner Form</t>
+          <t>Event Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>event_start_date</t>
+          <t>event_form_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Event Start Date</t>
+          <t>Event Description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_start_time</t>
+          <t>event_form_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Event Start Time</t>
+          <t>Event Location</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>event_form_start_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,64 +602,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>event_form_start_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>End Time</t>
+          <t>Start Time</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_duration</t>
+          <t>event_form_end_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Event Duration</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>event_form_end_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>End Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +671,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_description</t>
+          <t>event_form_duration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event Description</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,777 +694,87 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>event_form_organizer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event Location</t>
+          <t>Organizer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_form_created_by</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Created By</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_start_time</t>
+          <t>event_form_updated_by</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event Start Time</t>
+          <t>Updated By</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_end_date</t>
+          <t>event_form_notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event End Date</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>event_end_time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Event End Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>event_duration_in_hours</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Event Duration in Hours</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>event_duration_in_minutes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Event Duration in Minutes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>event_duration_in_hours</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Event Duration in Hours</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>event_start_date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Event Start Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>event_start_time</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Event Start Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>event_end_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Event End Date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_end_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Event End Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_duration</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Event Duration</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>event_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>event_description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Event Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>event_location</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Event Location</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>event_notes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Event Notes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>event_organizer</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Event Organizer</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>event_status</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Event Status</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>event_created_by</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Event Created By</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>event_created_on</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Event Created On</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>event_updated_by</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Event Updated By</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>event_updated_on</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Event Updated On</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>event_updated_at</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Event Updated At</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>event_last_updated_at</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Event Last Updated At</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>event_start_date</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Event Start Date</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>event_start_time</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Event Start Time</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>event_end_date</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Event End Date</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>event_end_time</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Event End Time</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>event_duration</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Event Duration</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>event_name</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>event_description</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Event Description</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>event_location</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Event Location</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>event_notes</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Event Notes</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
